--- a/public/datasets/tariffs-kazakhstan.xlsx
+++ b/public/datasets/tariffs-kazakhstan.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electricity_Tariffs_Almaty" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Water_Tariffs_Almaty" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions_for_Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Water_Consumption_Almaty_Annual" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +72,16 @@
       <color rgb="007B0000"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +113,12 @@
         <fgColor rgb="007B0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B5E3B"/>
+        <bgColor rgb="001B5E3B"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -167,6 +182,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1225,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1393,10 +1412,189 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Водоснабжение Алматы 2024 (годовой итог)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>234</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>млн м³ (год)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Водоснабжение Алматы 2019 (базовый год)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>143.1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>млн м³ (год)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Объём водоснабжения — Алматы (годовые данные)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>⚠ Данные по объёму водоснабжения г. Алматы из официальных отчётов ГКП «Алматы Су»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Год</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Объём водоснабжения (млн м³)</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Изм. к пред. году (%)</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B4" t="n">
+        <v>143.1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ГКП «Алматы Су», годовой отчёт 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B5" t="n">
+        <v>148</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>energyprom.kz / БНС РК (+3.1% к 2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B6" t="n">
+        <v>172</v>
+      </c>
+      <c r="C6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>kz.kursiv.media / Алматы Су</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B7" t="n">
+        <v>185</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>расчёт от 2021, Алматы Су</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" t="n">
+        <v>196</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>energyprom.kz (янв–май 101 млн м³, пересчёт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B9" t="n">
+        <v>234</v>
+      </c>
+      <c r="C9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>kz.kursiv.media / Алматы Су годовой отчёт 2024</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>